--- a/comp130-schedule-10-26-2025.xlsx
+++ b/comp130-schedule-10-26-2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmac\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmac\git\comp130-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83A6B15-72D4-409E-B7AD-DDF34DFFCD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D6D62F-5359-45E7-B406-682E1CC9F5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="classes" sheetId="1" r:id="rId1"/>
@@ -561,9 +561,6 @@
     <t>recursion with return values</t>
   </si>
   <si>
-    <t>1.7, 2.9, 3.9, 4.9, 5.12, 6.10, 7.7</t>
-  </si>
-  <si>
     <t>9.1-9.7</t>
   </si>
   <si>
@@ -801,6 +798,9 @@
       </rPr>
       <t>7.5-7.6</t>
     </r>
+  </si>
+  <si>
+    <t>1.7, 2.9, 3.9, 4.9, 5.12, 6.10</t>
   </si>
 </sst>
 </file>
@@ -1127,6 +1127,57 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1139,59 +1190,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1474,23 +1474,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="6.42578125" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.85546875" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" style="8" customWidth="1"/>
-    <col min="6" max="6" width="28.5703125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" customWidth="1"/>
+    <col min="3" max="3" width="7.26953125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.81640625" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="28.54296875" style="5" customWidth="1"/>
     <col min="7" max="7" width="14" style="8" customWidth="1"/>
-    <col min="8" max="8" width="25.85546875" style="5" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" customWidth="1"/>
-    <col min="11" max="11" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="6" customWidth="1"/>
-    <col min="17" max="17" width="11.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="25.81640625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="9.1796875" customWidth="1"/>
+    <col min="11" max="11" width="38.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.54296875" style="6" customWidth="1"/>
+    <col min="17" max="17" width="11.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="7" customFormat="1" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="7" customFormat="1" ht="50" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>4</v>
       </c>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="L1" s="9"/>
     </row>
-    <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="30">
         <v>1</v>
       </c>
@@ -1533,17 +1533,17 @@
       <c r="D2" s="12">
         <v>1</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="27" t="s">
         <v>44</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G2" s="15"/>
       <c r="H2" s="14"/>
       <c r="I2" s="12"/>
     </row>
-    <row r="3" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="30"/>
       <c r="B3" s="12" t="s">
         <v>1</v>
@@ -1556,26 +1556,26 @@
         <f t="shared" ref="D3:D27" si="0">D2+1</f>
         <v>2</v>
       </c>
-      <c r="E3" s="34"/>
+      <c r="E3" s="28"/>
       <c r="F3" s="14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G3" s="15" t="s">
         <v>98</v>
       </c>
       <c r="I3" s="12"/>
     </row>
-    <row r="4" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="30"/>
       <c r="B4" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="13">
         <f>C3+1</f>
         <v>45904</v>
       </c>
       <c r="D4" s="12"/>
-      <c r="E4" s="34"/>
+      <c r="E4" s="28"/>
       <c r="F4" s="14"/>
       <c r="G4" s="15"/>
       <c r="H4" s="14" t="s">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="I4" s="12"/>
     </row>
-    <row r="5" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="30"/>
       <c r="B5" s="12" t="s">
         <v>2</v>
@@ -1596,9 +1596,9 @@
         <f>D3+1</f>
         <v>3</v>
       </c>
-      <c r="E5" s="35"/>
+      <c r="E5" s="29"/>
       <c r="F5" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G5" s="15" t="s">
         <v>38</v>
@@ -1606,7 +1606,7 @@
       <c r="H5" s="14"/>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="30">
         <v>2</v>
       </c>
@@ -1622,11 +1622,11 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="27" t="s">
         <v>78</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G6" s="15" t="s">
         <v>127</v>
@@ -1636,7 +1636,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="30"/>
       <c r="B7" s="12" t="str">
         <f>B3</f>
@@ -1650,25 +1650,25 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="E7" s="34"/>
+      <c r="E7" s="28"/>
       <c r="F7" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="30"/>
       <c r="B8" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C8" s="13">
         <f>C7+1</f>
         <v>45911</v>
       </c>
       <c r="D8" s="12"/>
-      <c r="E8" s="34"/>
+      <c r="E8" s="28"/>
       <c r="F8" s="14"/>
       <c r="G8" s="15"/>
       <c r="H8" s="14" t="s">
@@ -1678,7 +1678,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="30"/>
       <c r="B9" s="12" t="str">
         <f t="shared" ref="B9" si="1">B5</f>
@@ -1692,9 +1692,9 @@
         <f>D7+1</f>
         <v>6</v>
       </c>
-      <c r="E9" s="35"/>
+      <c r="E9" s="29"/>
       <c r="F9" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G9" s="15" t="s">
         <v>124</v>
@@ -1702,7 +1702,7 @@
       <c r="H9" s="14"/>
       <c r="I9" s="12"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="30">
         <v>3</v>
       </c>
@@ -1718,7 +1718,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="26" t="s">
         <v>79</v>
       </c>
       <c r="F10" s="14" t="s">
@@ -1731,9 +1731,9 @@
       <c r="I10" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="Q10" s="29"/>
-    </row>
-    <row r="11" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q10" s="46"/>
+    </row>
+    <row r="11" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="30"/>
       <c r="B11" s="12" t="str">
         <f>B7</f>
@@ -1747,26 +1747,26 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E11" s="32"/>
+      <c r="E11" s="26"/>
       <c r="F11" s="14" t="s">
         <v>100</v>
       </c>
       <c r="G11" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="Q11" s="29"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q11" s="46"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="30"/>
       <c r="B12" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C12" s="13">
         <f>C11+1</f>
         <v>45918</v>
       </c>
       <c r="D12" s="12"/>
-      <c r="E12" s="32"/>
+      <c r="E12" s="26"/>
       <c r="F12" s="14"/>
       <c r="G12" s="15"/>
       <c r="H12" s="14" t="s">
@@ -1775,9 +1775,9 @@
       <c r="I12" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="Q12" s="29"/>
-    </row>
-    <row r="13" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q12" s="46"/>
+    </row>
+    <row r="13" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="30"/>
       <c r="B13" s="12" t="str">
         <f t="shared" ref="B13" si="2">B9</f>
@@ -1791,7 +1791,7 @@
         <f>D11+1</f>
         <v>9</v>
       </c>
-      <c r="E13" s="32"/>
+      <c r="E13" s="26"/>
       <c r="F13" s="14" t="s">
         <v>101</v>
       </c>
@@ -1800,9 +1800,9 @@
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="12"/>
-      <c r="Q13" s="29"/>
-    </row>
-    <row r="14" spans="1:17" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="Q13" s="46"/>
+    </row>
+    <row r="14" spans="1:17" ht="37" x14ac:dyDescent="0.35">
       <c r="A14" s="30">
         <v>4</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="30"/>
       <c r="B15" s="12" t="str">
         <f>B11</f>
@@ -1844,30 +1844,30 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="26" t="s">
         <v>81</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G15" s="15" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="30"/>
       <c r="B16" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C16" s="13">
         <f>C15+1</f>
         <v>45925</v>
       </c>
       <c r="D16" s="12"/>
-      <c r="E16" s="32"/>
+      <c r="E16" s="26"/>
       <c r="F16" s="14"/>
       <c r="G16" s="15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H16" s="14" t="s">
         <v>58</v>
@@ -1876,7 +1876,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="30"/>
       <c r="B17" s="12" t="str">
         <f t="shared" ref="B17" si="3">B13</f>
@@ -1890,17 +1890,17 @@
         <f>D15+1</f>
         <v>12</v>
       </c>
-      <c r="E17" s="32"/>
+      <c r="E17" s="26"/>
       <c r="F17" s="14" t="s">
         <v>102</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H17" s="14"/>
       <c r="I17" s="12"/>
     </row>
-    <row r="18" spans="1:9" ht="65.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="40" x14ac:dyDescent="0.35">
       <c r="A18" s="30">
         <v>5</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="30"/>
       <c r="B19" s="12" t="str">
         <f>B15</f>
@@ -1942,27 +1942,27 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="26" t="s">
         <v>80</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="30"/>
       <c r="B20" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C20" s="13">
         <f>C19+1</f>
         <v>45932</v>
       </c>
       <c r="D20" s="12"/>
-      <c r="E20" s="32"/>
+      <c r="E20" s="26"/>
       <c r="F20" s="14"/>
       <c r="G20" s="15"/>
       <c r="H20" s="14" t="s">
@@ -1972,7 +1972,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="30"/>
       <c r="B21" s="12" t="str">
         <f>B17</f>
@@ -1986,17 +1986,17 @@
         <f>D19+1</f>
         <v>15</v>
       </c>
-      <c r="E21" s="32"/>
+      <c r="E21" s="26"/>
       <c r="F21" s="20" t="s">
         <v>104</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="12"/>
     </row>
-    <row r="22" spans="1:9" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="50" x14ac:dyDescent="0.35">
       <c r="A22" s="30">
         <v>6</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="30"/>
       <c r="B23" s="12" t="str">
         <f>B19</f>
@@ -2045,10 +2045,10 @@
       <c r="G23" s="15"/>
       <c r="I23" s="12"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="30"/>
       <c r="B24" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C24" s="13">
         <f>C23+1</f>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="I24" s="12"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="30"/>
       <c r="B25" s="12" t="str">
         <f t="shared" ref="B25" si="4">B21</f>
@@ -2085,7 +2085,7 @@
       <c r="H25" s="14"/>
       <c r="I25" s="12"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="30">
         <v>7</v>
       </c>
@@ -2101,8 +2101,8 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="E26" s="32" t="s">
-        <v>147</v>
+      <c r="E26" s="26" t="s">
+        <v>146</v>
       </c>
       <c r="F26" s="14" t="s">
         <v>42</v>
@@ -2115,7 +2115,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="30"/>
       <c r="B27" s="12" t="str">
         <f>B23</f>
@@ -2129,7 +2129,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="E27" s="32"/>
+      <c r="E27" s="26"/>
       <c r="F27" s="14" t="s">
         <v>130</v>
       </c>
@@ -2138,17 +2138,17 @@
       </c>
       <c r="I27" s="12"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="30"/>
       <c r="B28" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C28" s="13">
         <f>C27+1</f>
         <v>45946</v>
       </c>
       <c r="D28" s="12"/>
-      <c r="E28" s="32"/>
+      <c r="E28" s="26"/>
       <c r="F28" s="14"/>
       <c r="G28" s="15"/>
       <c r="H28" s="17" t="s">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="I28" s="12"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="30"/>
       <c r="B29" s="12" t="str">
         <f t="shared" ref="B29" si="5">B25</f>
@@ -2170,7 +2170,7 @@
         <f>D27+1</f>
         <v>21</v>
       </c>
-      <c r="E29" s="32"/>
+      <c r="E29" s="26"/>
       <c r="F29" s="14" t="s">
         <v>131</v>
       </c>
@@ -2180,22 +2180,22 @@
       <c r="H29" s="14"/>
       <c r="I29" s="12"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="30">
         <v>8</v>
       </c>
-      <c r="B30" s="31" t="s">
+      <c r="B30" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="37"/>
-      <c r="I30" s="38"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C30" s="47"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="33"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="30"/>
       <c r="B31" s="12" t="str">
         <f>B27</f>
@@ -2209,19 +2209,19 @@
         <f>D29+1</f>
         <v>22</v>
       </c>
-      <c r="E31" s="32"/>
+      <c r="E31" s="26"/>
       <c r="F31" s="20" t="s">
         <v>95</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I31" s="12"/>
     </row>
-    <row r="32" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="30"/>
       <c r="B32" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C32" s="13">
         <f>C31+1</f>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="I32" s="12"/>
     </row>
-    <row r="33" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A33" s="30"/>
       <c r="B33" s="12" t="str">
         <f t="shared" ref="B33" si="6">B29</f>
@@ -2250,21 +2250,21 @@
         <f>D31+1</f>
         <v>23</v>
       </c>
-      <c r="E33" s="32" t="s">
+      <c r="E33" s="26" t="s">
         <v>83</v>
       </c>
       <c r="F33" s="14" t="s">
         <v>106</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H33" s="14"/>
       <c r="I33" s="12" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="30">
         <v>9</v>
       </c>
@@ -2280,17 +2280,17 @@
         <f t="shared" ref="D34:D50" si="7">D33+1</f>
         <v>24</v>
       </c>
-      <c r="E34" s="32"/>
+      <c r="E34" s="26"/>
       <c r="F34" s="14" t="s">
         <v>108</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H34" s="14"/>
       <c r="I34" s="12"/>
     </row>
-    <row r="35" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="30"/>
       <c r="B35" s="12" t="str">
         <f>B31</f>
@@ -2304,18 +2304,18 @@
         <f t="shared" si="7"/>
         <v>25</v>
       </c>
-      <c r="E35" s="32"/>
+      <c r="E35" s="26"/>
       <c r="F35" s="14" t="s">
         <v>107</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="30"/>
       <c r="B36" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C36" s="13">
         <f>C35+1</f>
@@ -2332,7 +2332,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="30"/>
       <c r="B37" s="12" t="str">
         <f t="shared" ref="B37" si="8">B33</f>
@@ -2346,21 +2346,21 @@
         <f>D35+1</f>
         <v>26</v>
       </c>
-      <c r="E37" s="33" t="s">
+      <c r="E37" s="27" t="s">
         <v>84</v>
       </c>
       <c r="F37" s="14" t="s">
         <v>109</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H37" s="14"/>
       <c r="I37" s="12" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="30">
         <v>10</v>
       </c>
@@ -2376,17 +2376,17 @@
         <f t="shared" si="7"/>
         <v>27</v>
       </c>
-      <c r="E38" s="34"/>
+      <c r="E38" s="28"/>
       <c r="F38" s="14" t="s">
         <v>110</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H38" s="14"/>
       <c r="I38" s="12"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="30"/>
       <c r="B39" s="12" t="str">
         <f>B35</f>
@@ -2400,7 +2400,7 @@
         <f t="shared" si="7"/>
         <v>28</v>
       </c>
-      <c r="E39" s="35"/>
+      <c r="E39" s="29"/>
       <c r="F39" s="14" t="s">
         <v>102</v>
       </c>
@@ -2409,10 +2409,10 @@
       </c>
       <c r="I39" s="12"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="30"/>
       <c r="B40" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C40" s="13">
         <f>C39+1</f>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="I40" s="12"/>
     </row>
-    <row r="41" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="30"/>
       <c r="B41" s="12" t="str">
         <f t="shared" ref="B41" si="9">B37</f>
@@ -2441,21 +2441,21 @@
         <f>D39+1</f>
         <v>29</v>
       </c>
-      <c r="E41" s="33" t="s">
+      <c r="E41" s="27" t="s">
         <v>85</v>
       </c>
       <c r="F41" s="14" t="s">
         <v>111</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H41" s="14"/>
       <c r="I41" s="12" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="30">
         <v>11</v>
       </c>
@@ -2471,17 +2471,17 @@
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
-      <c r="E42" s="35"/>
+      <c r="E42" s="29"/>
       <c r="F42" s="14" t="s">
         <v>112</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H42" s="14"/>
       <c r="I42" s="12"/>
     </row>
-    <row r="43" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="30"/>
       <c r="B43" s="12" t="str">
         <f>B39</f>
@@ -2495,27 +2495,27 @@
         <f t="shared" si="7"/>
         <v>31</v>
       </c>
-      <c r="E43" s="32" t="s">
+      <c r="E43" s="26" t="s">
         <v>86</v>
       </c>
       <c r="F43" s="14" t="s">
         <v>113</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="30"/>
       <c r="B44" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C44" s="13">
         <f>C43+1</f>
         <v>45974</v>
       </c>
       <c r="D44" s="12"/>
-      <c r="E44" s="32"/>
+      <c r="E44" s="26"/>
       <c r="F44" s="14"/>
       <c r="G44" s="15"/>
       <c r="H44" s="14" t="s">
@@ -2525,7 +2525,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A45" s="30"/>
       <c r="B45" s="12" t="str">
         <f t="shared" ref="B45" si="10">B41</f>
@@ -2539,19 +2539,19 @@
         <f>D43+1</f>
         <v>32</v>
       </c>
-      <c r="E45" s="32"/>
+      <c r="E45" s="26"/>
       <c r="F45" s="14" t="s">
         <v>114</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H45" s="14"/>
       <c r="I45" s="12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="30">
         <v>12</v>
       </c>
@@ -2567,17 +2567,17 @@
         <f t="shared" si="7"/>
         <v>33</v>
       </c>
-      <c r="E46" s="32"/>
+      <c r="E46" s="26"/>
       <c r="F46" s="14" t="s">
         <v>115</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H46" s="14"/>
       <c r="I46" s="12"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="30"/>
       <c r="B47" s="12" t="str">
         <f>B43</f>
@@ -2600,10 +2600,10 @@
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" s="30"/>
       <c r="B48" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C48" s="13">
         <f>C47+1</f>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="I48" s="12"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="30"/>
       <c r="B49" s="12" t="str">
         <f t="shared" ref="B49" si="11">B45</f>
@@ -2640,7 +2640,7 @@
       <c r="H49" s="14"/>
       <c r="I49" s="12"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="30">
         <v>13</v>
       </c>
@@ -2656,45 +2656,45 @@
         <f t="shared" si="7"/>
         <v>36</v>
       </c>
-      <c r="E50" s="32" t="s">
+      <c r="E50" s="26" t="s">
         <v>87</v>
       </c>
       <c r="F50" s="14" t="s">
         <v>118</v>
       </c>
       <c r="G50" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H50" s="14"/>
       <c r="I50" s="12" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="30"/>
-      <c r="B51" s="31" t="s">
+      <c r="B51" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="31"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="32"/>
-      <c r="F51" s="39"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="40"/>
-      <c r="I51" s="41"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C51" s="47"/>
+      <c r="D51" s="47"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="34"/>
+      <c r="G51" s="35"/>
+      <c r="H51" s="35"/>
+      <c r="I51" s="36"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="30"/>
-      <c r="B52" s="31"/>
-      <c r="C52" s="31"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="32"/>
-      <c r="F52" s="42"/>
-      <c r="G52" s="43"/>
-      <c r="H52" s="43"/>
-      <c r="I52" s="44"/>
-    </row>
-    <row r="53" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B52" s="47"/>
+      <c r="C52" s="47"/>
+      <c r="D52" s="47"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="37"/>
+      <c r="G52" s="38"/>
+      <c r="H52" s="38"/>
+      <c r="I52" s="39"/>
+    </row>
+    <row r="53" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A53" s="30">
         <v>14</v>
       </c>
@@ -2710,17 +2710,17 @@
         <f>D50+1</f>
         <v>37</v>
       </c>
-      <c r="E53" s="32"/>
+      <c r="E53" s="26"/>
       <c r="F53" s="14" t="s">
         <v>116</v>
       </c>
       <c r="G53" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H53" s="14"/>
       <c r="I53" s="12"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="30"/>
       <c r="B54" s="12" t="str">
         <f>B47</f>
@@ -2734,19 +2734,19 @@
         <f>D53+1</f>
         <v>38</v>
       </c>
-      <c r="E54" s="32"/>
+      <c r="E54" s="26"/>
       <c r="F54" s="14" t="s">
         <v>117</v>
       </c>
       <c r="G54" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I54" s="12"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="30"/>
       <c r="B55" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C55" s="13">
         <f>C54+1</f>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="I55" s="12"/>
     </row>
-    <row r="56" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A56" s="30"/>
       <c r="B56" s="12" t="str">
         <f>B49</f>
@@ -2775,11 +2775,11 @@
         <f>D54+1</f>
         <v>39</v>
       </c>
-      <c r="E56" s="32" t="s">
+      <c r="E56" s="26" t="s">
         <v>88</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G56" s="15"/>
       <c r="H56" s="14"/>
@@ -2787,7 +2787,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="30">
         <v>15</v>
       </c>
@@ -2803,15 +2803,15 @@
         <f>D56+1</f>
         <v>40</v>
       </c>
-      <c r="E57" s="32"/>
-      <c r="F57" s="45" t="s">
+      <c r="E57" s="26"/>
+      <c r="F57" s="40" t="s">
         <v>103</v>
       </c>
       <c r="G57" s="15"/>
       <c r="H57" s="14"/>
       <c r="I57" s="12"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="30"/>
       <c r="B58" s="12" t="str">
         <f>B54</f>
@@ -2825,30 +2825,30 @@
         <f>D57+1</f>
         <v>41</v>
       </c>
-      <c r="E58" s="32"/>
-      <c r="F58" s="46"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="41"/>
       <c r="G58" s="15"/>
       <c r="I58" s="22"/>
     </row>
-    <row r="59" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A59" s="30"/>
       <c r="B59" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C59" s="13">
         <f>C58+1</f>
         <v>46002</v>
       </c>
       <c r="D59" s="12"/>
-      <c r="E59" s="32"/>
-      <c r="F59" s="46"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="41"/>
       <c r="G59" s="15"/>
       <c r="H59" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I59" s="22"/>
     </row>
-    <row r="60" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="30"/>
       <c r="B60" s="12" t="str">
         <f t="shared" ref="B60" si="12">B56</f>
@@ -2862,15 +2862,15 @@
         <f>D58+1</f>
         <v>42</v>
       </c>
-      <c r="E60" s="32"/>
-      <c r="F60" s="47"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="42"/>
       <c r="G60" s="15"/>
       <c r="H60" s="14"/>
       <c r="I60" s="14" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="18">
         <v>16</v>
       </c>
@@ -2880,35 +2880,17 @@
       <c r="C61" s="13">
         <v>46007</v>
       </c>
-      <c r="D61" s="26" t="s">
+      <c r="D61" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="E61" s="27"/>
-      <c r="F61" s="28"/>
+      <c r="E61" s="44"/>
+      <c r="F61" s="45"/>
       <c r="G61" s="15"/>
       <c r="H61" s="14"/>
       <c r="I61" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="E10:E13"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="E26:E31"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="E6:E9"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="E56:E60"/>
-    <mergeCell ref="E50:E54"/>
-    <mergeCell ref="F30:I30"/>
-    <mergeCell ref="F51:I52"/>
-    <mergeCell ref="E43:E46"/>
-    <mergeCell ref="F57:F60"/>
     <mergeCell ref="D61:F61"/>
     <mergeCell ref="Q10:Q13"/>
     <mergeCell ref="A50:A52"/>
@@ -2925,6 +2907,24 @@
     <mergeCell ref="A22:A25"/>
     <mergeCell ref="E33:E35"/>
     <mergeCell ref="E37:E39"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="E56:E60"/>
+    <mergeCell ref="E50:E54"/>
+    <mergeCell ref="F30:I30"/>
+    <mergeCell ref="F51:I52"/>
+    <mergeCell ref="E43:E46"/>
+    <mergeCell ref="F57:F60"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="E26:E31"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="E6:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
@@ -2934,13 +2934,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2713FC8-F94B-4307-A10A-C839F1616476}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="30.140625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.1796875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="30.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D1" s="5" t="s">
         <v>33</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -3000,7 +3000,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -3105,7 +3105,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -3218,7 +3218,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
